--- a/astro-site/public/dl/chocolate-shop-checklist-templates/01-chocolate-shop-opening-closing-checklists.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/01-chocolate-shop-opening-closing-checklists.xlsx
@@ -710,14 +710,14 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>▸ The cool room and fridges are not "turned on": check that they ran all night and log the reading. Targets for this trade: kitchen 64–68 °F, cool room 59–64 °F at 50–60% humidity, fillings and ganaches 41 °F or below, bonbon display case 60–64 °F.</t>
+          <t>▸ The cool room and fridges are not "turned on": check that they ran all night and log the reading. Targets for this trade: kitchen 64–68 °F, cool room 59–64 °F at 50–60% humidity, fillings and ganaches 41 °F or below, bonbon display case 60–64 °F. Fresh-cream ganache is TCS unless a lab test says otherwise: it does not go in the 60–64 °F case.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>▸ Above 68 °F cocoa butter starts to melt: the bonbon sweats, loses its shine and within two days fat bloom shows up. That is why the display case gets its own check.</t>
+          <t>▸ Above 68 °F chocolate softens and bloom risk climbs: the bonbon sweats, loses its shine and within two days fat bloom shows up. That is why the display case gets its own check.</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Anyone with vomiting, diarrhea, jaundice, sore throat with fever or an infected wound does NOT handle food: tell the shift lead and reassign the task (FDA 2-201.11)</t>
+          <t>Vomiting, diarrhea or jaundice: that person does NOT work today — send them home (exclusion) and the person in charge reports jaundice or a diagnosed illness to the health department; sore throat with fever or an uncovered infected wound: reassign away from unwrapped food (FDA 2-201.11, 2-201.12)</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Turn on the tempering machine and preheat to 113 °F</t>
+          <t>Turn on the tempering machine and preheat per the manufacturer (typically 113 °F)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Check the bonbon display case holds 60–64 °F and is not fogging up before setting out product (above 68 °F cocoa butter melts and bonbons lose their shine) — log reading: ____ °F</t>
+          <t>Check the bonbon display case has reached 60–64 °F (it is switched on when you arrive) and is not fogging up before setting out product (above 68 °F chocolate softens and bonbons lose their shine) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Turn on the A/C — keep the shop at 68–72 °F</t>
+          <t>Turn on the A/C — keep the shop at 68–72 °F (unwrapped bonbons stay in the 60–64 °F case)</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Service setup</t>
+          <t>Shop and display setup</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Set up the display case: bonbons, bars, molded figures, truffles</t>
+          <t>Set up the display case: bonbons, bars, molded figures, truffles — fresh-cream (TCS) items only if lab-tested as non-TCS; otherwise in a refrigerated case at 41 °F or below (shelf life table in file 02)</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Set up the sample station with the day's samples: tongs, toothpicks or single-use cups, never bare hands (FDA 3-301.11)</t>
+          <t>Set up the sample station with the day's samples: one set of tongs per tray (nut and peanut items never share tongs), toothpicks or single-use cups, never bare hands (FDA 3-301.11)</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Take product out of the display case and store it in the cool room</t>
+          <t>Take product out of the display case: bonbons and bars to the cool room; any TCS fresh-cream item to the fridge (41 °F or below)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Make sure gas burners are off (the main valve is for emergencies only) and that water and lights are off</t>
+          <t>Make sure gas burners are off (the main valve is for emergencies only), no taps are left running and lights are off</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
